--- a/AutoXP3_samples_split/Sample3.xlsx
+++ b/AutoXP3_samples_split/Sample3.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,19 +11,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -52,7 +58,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,7 +422,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -478,7 +484,6 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,7 +508,6 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,18 +515,14 @@
           <t>Y1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&gt;0</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -567,13 +567,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>5.28</v>
       </c>
       <c r="D2" t="n">
-        <v>13.42405902772773</v>
+        <v>-7.2674</v>
       </c>
     </row>
     <row r="3">
@@ -581,13 +581,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="D3" t="n">
-        <v>4.491932699304051</v>
+        <v>-4.8815</v>
       </c>
     </row>
     <row r="4">
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6.81</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>2.99</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.140464684812803</v>
+        <v>-5.8138</v>
       </c>
     </row>
     <row r="5">
@@ -609,13 +609,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>6.81</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2.16</v>
       </c>
       <c r="D5" t="n">
-        <v>-6.526406427233821</v>
+        <v>-0.3259</v>
       </c>
     </row>
     <row r="6">
@@ -623,13 +623,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.511142913818915</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="7">
@@ -637,13 +637,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3.87</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.159719516772654</v>
+        <v>1.6568</v>
       </c>
     </row>
     <row r="8">
@@ -651,13 +651,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>3.74</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>3.83</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.126331265818484</v>
+        <v>-3.5578</v>
       </c>
     </row>
     <row r="9">
@@ -665,13 +665,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>7.58</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4.81</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2443547893775199</v>
+        <v>-20.6986</v>
       </c>
     </row>
     <row r="10">
@@ -679,13 +679,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2.46</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6.42</v>
       </c>
       <c r="D10" t="n">
-        <v>8.06520442129516</v>
+        <v>-4.2211</v>
       </c>
     </row>
     <row r="11">
@@ -693,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>6.81</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="D11" t="n">
-        <v>18.1866425471083</v>
+        <v>-18.7041</v>
       </c>
     </row>
   </sheetData>
@@ -714,7 +714,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
+  <cols>
+    <col width="15.81640625" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
